--- a/pack/DirectSportsGoods_acquisition.xlsx
+++ b/pack/DirectSportsGoods_acquisition.xlsx
@@ -2959,58 +2959,58 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>5323975.35</v>
+        <v>6163240.79</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>5294933.41</v>
+        <v>6209957.67</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>5289266.6</v>
+        <v>6282121.46</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>4703990.74</v>
+        <v>5720279.2</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4745300</v>
+        <v>5869759.66</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>4849753.21</v>
+        <v>6082237.88</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>5024143.69</v>
+        <v>6298108.81</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>5216220.86</v>
+        <v>6588375.43</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>5355110.4</v>
+        <v>6817086.9</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>5516998.49</v>
+        <v>7017745.22</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>5916143.87</v>
+        <v>7536411.94</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>5968751.84</v>
+        <v>7693510.3</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>4512818.17</v>
+        <v>6240314.24</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>4497103.82</v>
+        <v>6305737.58</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>4514448.46</v>
+        <v>6406438.8</v>
       </c>
       <c r="Q6" s="10" t="n">
-        <v>4520936.84</v>
+        <v>6438208.6</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>4903673.73</v>
+        <v>6936796.85</v>
       </c>
       <c r="S6" s="10" t="n">
-        <v>5354771.69</v>
+        <v>7503589.6</v>
       </c>
       <c r="T6" s="10">
         <f>MIN(B6:S6)</f>
@@ -3024,58 +3024,58 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>5323975.35</v>
+        <v>6163240.79</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>5294933.41</v>
+        <v>6209957.67</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5289266.6</v>
+        <v>6282121.46</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>4703990.74</v>
+        <v>5720279.2</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>4745300</v>
+        <v>5869759.66</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>4849753.21</v>
+        <v>6082237.88</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>5024143.69</v>
+        <v>6298108.81</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>5216220.86</v>
+        <v>6588375.43</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>5355110.4</v>
+        <v>6817086.9</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>5516998.49</v>
+        <v>7017745.22</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>5916143.87</v>
+        <v>7536411.94</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>5962291.44</v>
+        <v>7687049.91</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>5748820.64</v>
+        <v>7476316.71</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>5725569.16</v>
+        <v>7534202.92</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>5734299.94</v>
+        <v>7626290.28</v>
       </c>
       <c r="Q7" s="10" t="n">
-        <v>5730020.98</v>
+        <v>7647292.75</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>6100913.81</v>
+        <v>8134036.93</v>
       </c>
       <c r="S7" s="10" t="n">
-        <v>6540167.71</v>
+        <v>8688985.619999999</v>
       </c>
       <c r="T7" s="10">
         <f>MIN(B7:S7)</f>
@@ -3089,58 +3089,58 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>5201607.11</v>
+        <v>6033302.86</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>5039960.29</v>
+        <v>5939313.08</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>4892435.22</v>
+        <v>5861296.49</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>4140640.56</v>
+        <v>5123107.82</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3984282.17</v>
+        <v>5063342.12</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3882320.66</v>
+        <v>5057858.48</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>4019327.57</v>
+        <v>5297295.23</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>4024519.28</v>
+        <v>5390170.44</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>3984425.19</v>
+        <v>5430295.09</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>4107518.69</v>
+        <v>5653394.81</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>4277319.15</v>
+        <v>5929946.03</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>4157093</v>
+        <v>5903048.2</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>2673551.73</v>
+        <v>4480949.31</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>2437529.78</v>
+        <v>4310554.69</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>2219301.77</v>
+        <v>4159749.9</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>2125593.98</v>
+        <v>4145712.17</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>2181809.31</v>
+        <v>4295622.4</v>
       </c>
       <c r="S8" s="10" t="n">
-        <v>2290115.24</v>
+        <v>4497511.87</v>
       </c>
       <c r="T8" s="10">
         <f>MIN(B8:S8)</f>
@@ -3154,58 +3154,58 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>5201607.11</v>
+        <v>6033302.86</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>5039960.29</v>
+        <v>5939313.08</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>4892435.22</v>
+        <v>5861296.49</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>4140640.56</v>
+        <v>5123107.82</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>3984282.17</v>
+        <v>5063342.12</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>3882320.66</v>
+        <v>5057858.48</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>4019327.57</v>
+        <v>5297295.23</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>4024519.28</v>
+        <v>5390170.44</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>3984425.19</v>
+        <v>5430295.09</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>4107518.69</v>
+        <v>5653394.81</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>4277319.15</v>
+        <v>5929946.03</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>4150632.6</v>
+        <v>5896587.8</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>3909554.2</v>
+        <v>5716951.78</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>3665995.12</v>
+        <v>5539020.03</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>3439153.24</v>
+        <v>5379601.38</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>3334678.12</v>
+        <v>5354796.31</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>3379049.39</v>
+        <v>5492862.49</v>
       </c>
       <c r="S9" s="10" t="n">
-        <v>3475511.26</v>
+        <v>5682907.89</v>
       </c>
       <c r="T9" s="10">
         <f>MIN(B9:S9)</f>
@@ -3219,58 +3219,58 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>5402627.9</v>
+        <v>6247029.07</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>5459119.47</v>
+        <v>6384783.38</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>5542936.37</v>
+        <v>6552083.93</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>5063119.54</v>
+        <v>6102373.66</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>5230030.18</v>
+        <v>6385326.49</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>5465904.22</v>
+        <v>6737067.51</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>5671723.51</v>
+        <v>6987378.24</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>5982452.8</v>
+        <v>7403436.82</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>6235695.46</v>
+        <v>7753024.08</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>6429754</v>
+        <v>7988670.69</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>6974469.18</v>
+        <v>8661577.4</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>7132797.47</v>
+        <v>8931973.029999999</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>5721074.06</v>
+        <v>7527887.05</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>5867390.25</v>
+        <v>7766273.92</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>6053624.03</v>
+        <v>8047094.68</v>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>6155703.07</v>
+        <v>8182401.74</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>6776951.09</v>
+        <v>8935125.57</v>
       </c>
       <c r="S10" s="10" t="n">
-        <v>7478029.8</v>
+        <v>9767481.560000001</v>
       </c>
       <c r="T10" s="10">
         <f>MIN(B10:S10)</f>
@@ -3284,58 +3284,58 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>5402627.9</v>
+        <v>6247029.07</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5459119.47</v>
+        <v>6384783.38</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5542936.37</v>
+        <v>6552083.93</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5063119.54</v>
+        <v>6102373.66</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5230030.18</v>
+        <v>6385326.49</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5465904.22</v>
+        <v>6737067.51</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>5671723.51</v>
+        <v>6987378.24</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>5982452.8</v>
+        <v>7403436.82</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>6235695.46</v>
+        <v>7753024.08</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>6429754</v>
+        <v>7988670.69</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>6974469.18</v>
+        <v>8661577.4</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>7126337.07</v>
+        <v>8925512.630000001</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>6957076.53</v>
+        <v>8763889.52</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>7095855.59</v>
+        <v>8994739.26</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>7273475.5</v>
+        <v>9266946.15</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>7364787.21</v>
+        <v>9391485.890000001</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>7974191.18</v>
+        <v>10132365.65</v>
       </c>
       <c r="S11" s="10" t="n">
-        <v>8663425.82</v>
+        <v>10952877.58</v>
       </c>
       <c r="T11" s="10">
         <f>MIN(B11:S11)</f>
